--- a/prep_and_checklists/A24  /PLATEWARE PULL SHEET A24  _Friday, March 20, 2026  _0.xlsx
+++ b/prep_and_checklists/A24  /PLATEWARE PULL SHEET A24  _Friday, March 20, 2026  _0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/prep_and_checklists/A24  /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D173E3A-A5CB-7B42-935C-24A23315F228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D6DFC3-A802-E94E-BBE1-79A83BB6106F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="980" windowWidth="29940" windowHeight="17600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="105">
   <si>
     <t xml:space="preserve">Event: A24   Date: Friday, March 20, 2026  </t>
   </si>
@@ -3965,8 +3965,12 @@
       <c r="A5" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="92"/>
-      <c r="C5" s="93"/>
+      <c r="B5" s="92">
+        <v>8</v>
+      </c>
+      <c r="C5" s="93" t="s">
+        <v>104</v>
+      </c>
       <c r="D5" s="69"/>
       <c r="E5" s="35" t="s">
         <v>9</v>
